--- a/stories/arbres/ATOM-REL.AMI.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gabrielle est dans le jardin. Maman est près des pots. Gabrielle a une corde à sauter. Noé est près du cerisier. Gabrielle va vers lui. Elle dit : tu veux jouer avec nous ? Inviter, c'est demander. Noé dit : non. Gabrielle s'arrête. Elle accepte le non. Un non est possible. Maman dit : tu as su inviter. Tu as su accepter un non. Parce qu'elle accepte, Noé reste tranquille. Gabrielle saute seule. La corde claque doucement. Plus tard, Iris passe. Gabrielle invite encore. Iris dit : oui. Elles sautent. Le non de Noé est entendu. Papa les rejoindra pour le goûter.</t>
+          <t>Gabrielle est dans le jardin. Maman est près des pots. Gabrielle a une corde à sauter. Noé est près du cerisier. Gabrielle va vers lui. Tu veux jouer avec nous ? Inviter, c'est demander. Non. Gabrielle s'arrête. Elle accepte le non. Un non est possible. Tu as su inviter. Tu as su accepter un non. Parce qu'elle accepte, Noé reste tranquille. Gabrielle saute seule. La corde claque doucement. Plus tard, Iris passe. Gabrielle invite encore. Oui. Elles sautent. Le non de Noé est entendu. Papa les rejoindra pour le goûter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gabrielle est dans le jardin. Maman est près des pots. Gabrielle a une corde à sauter. Noé est près du cerisier. Gabrielle va vers lui.
+narrateur|Tu veux jouer avec nous ? Inviter, c'est demander.
+copain|Non.
+narrateur|Gabrielle s'arrête. Elle accepte le non. Un non est possible.
+maman|Tu as su inviter. Tu as su accepter un non. Parce qu'elle accepte, Noé reste tranquille.
+narrateur|Gabrielle saute seule. La corde claque doucement. Plus tard, Iris passe. Gabrielle invite encore.
+copine|Oui. Elles sautent.
+narrateur|Le non de Noé est entendu. Papa les rejoindra pour le goûter.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé dit non. Que fait Gabrielle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gabrielle a su inviter. Elle a accepté le non. Maman a vu. Un non est possible.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gabrielle range la corde. Maman lui tend le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Le non de Noé est entendu. Papa les rejoindra pour le goûter.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Noé dit non. Que fait Gabrielle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Gabrielle a su inviter. Elle a accepté le non. Maman a vu. Un non est possible.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1846,7 @@
           <t>narrateur|Gabrielle range la corde. Maman lui tend le sac.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.AMI.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gabrielle invite et accepte un non</t>
+          <t>La corde de Mila</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila invite Victorino à sauter à la corde. Victorino dit non. Mila accepte et saute avec maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gabrielle est dans le jardin. Maman est près des pots. Gabrielle a une corde à sauter. Noé est près du cerisier. Gabrielle va vers lui. Tu veux jouer avec nous ? Inviter, c'est demander. Non. Gabrielle s'arrête. Elle accepte le non. Un non est possible. Tu as su inviter. Tu as su accepter un non. Parce qu'elle accepte, Noé reste tranquille. Gabrielle saute seule. La corde claque doucement. Plus tard, Iris passe. Gabrielle invite encore. Oui. Elles sautent. Le non de Noé est entendu. Papa les rejoindra pour le goûter.</t>
+          <t>Une cerise bien rouge pend au cerisier. Les pots en terre sont chauds. Une coccinelle marche sur une feuille. L'arrosoir de maman goutte encore. Une goutte fait un rond dans la terre. Ça sent la terre mouillée. Mila, tu as vu la cerise ? Elle est toute rouge. Oui. Elle est trop haute. En ce moment, Mila tient une corde. La corde est un peu rêche. Les poignées sont en bois lisse. Je veux sauter. On saute dans l'herbe, d'accord. Victorino est sous le cerisier. Il regarde la coccinelle. La feuille tremble un peu. Tu peux inviter. Inviter, c'est demander. Mila va vers lui. Tu veux jouer avec nous ? Victorino secoue la tête. Non. Mila s'arrête. La corde reste dans ses mains. Maman pose l'arrosoir. On peut accepter un non. Accepter un non, c'est possible. D'accord. Mila reste dans l'herbe. Elle saute avec maman. La corde claque doucement. L'herbe est fraîche sous les pieds. Tu sautes bien. Ça fait un bruit. Oui. Un petit clac. Victorino reste sous le cerisier. La coccinelle avance encore. Mila accepte le non. Victorino reste tranquille. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On saute encore un peu ? Oui, maman. Une autre goutte tombe. Ça sent toujours la terre. Tu as fini de sauter ? Oui. Bravo. Tu as fait du bon travail. Mila pose la corde. La cerise pend encore, bien rouge.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gabrielle est dans le jardin. Maman est près des pots. Gabrielle a une corde à sauter. Noé est près du cerisier. Gabrielle va vers lui.
-narrateur|Tu veux jouer avec nous ? Inviter, c'est demander.
+          <t>narrateur|Une cerise bien rouge pend au cerisier.
+narrateur|Les pots en terre sont chauds.
+narrateur|Une coccinelle marche sur une feuille.
+narrateur|L'arrosoir de maman goutte encore.
+narrateur|Une goutte fait un rond dans la terre.
+narrateur|Ça sent la terre mouillée.
+maman|Mila, tu as vu la cerise ?
+enfant-f|Elle est toute rouge.
+maman|Oui.
+maman|Elle est trop haute.
+narrateur|En ce moment, Mila tient une corde.
+narrateur|La corde est un peu rêche.
+narrateur|Les poignées sont en bois lisse.
+enfant-f|Je veux sauter.
+maman|On saute dans l'herbe, d'accord.
+narrateur|Victorino est sous le cerisier.
+narrateur|Il regarde la coccinelle.
+narrateur|La feuille tremble un peu.
+maman|Tu peux inviter.
+maman|Inviter, c'est demander.
+narrateur|Mila va vers lui.
+enfant-f|Tu veux jouer avec nous ?
+narrateur|Victorino secoue la tête.
 copain|Non.
-narrateur|Gabrielle s'arrête. Elle accepte le non. Un non est possible.
-maman|Tu as su inviter. Tu as su accepter un non. Parce qu'elle accepte, Noé reste tranquille.
-narrateur|Gabrielle saute seule. La corde claque doucement. Plus tard, Iris passe. Gabrielle invite encore.
-copine|Oui. Elles sautent.
-narrateur|Le non de Noé est entendu. Papa les rejoindra pour le goûter.</t>
+narrateur|Mila s'arrête.
+narrateur|La corde reste dans ses mains.
+narrateur|Maman pose l'arrosoir.
+maman|On peut accepter un non.
+maman|Accepter un non, c'est possible.
+enfant-f|D'accord.
+narrateur|Mila reste dans l'herbe.
+narrateur|Elle saute avec maman.
+narrateur|La corde claque doucement.
+narrateur|L'herbe est fraîche sous les pieds.
+maman|Tu sautes bien.
+enfant-f|Ça fait un bruit.
+maman|Oui.
+maman|Un petit clac.
+narrateur|Victorino reste sous le cerisier.
+narrateur|La coccinelle avance encore.
+narrateur|Mila accepte le non.
+narrateur|Victorino reste tranquille.
+maman|Merci.
+maman|Tu as su inviter.
+maman|Tu as su accepter un non.
+enfant-f|Il a dit non.
+maman|Un non, c'est possible.
+maman|On saute encore un peu ?
+enfant-f|Oui, maman.
+narrateur|Une autre goutte tombe.
+narrateur|Ça sent toujours la terre.
+maman|Tu as fini de sauter ?
+enfant-f|Oui.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Mila pose la corde.
+narrateur|La cerise pend encore, bien rouge.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé dit non. Que fait Gabrielle ?</t>
+          <t>Victorino dit non. Que fait Mila ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,10 +1568,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé dit non. Que fait Gabrielle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino dit non.
+narrateur|Que fait Mila ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gabrielle a su inviter. Elle a accepté le non. Maman a vu. Un non est possible.</t>
+          <t>Mila a demandé. C'est inviter. Victorino a dit non. Mila a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Mila. J'ai dit d'accord. Oui. Un non, c'est possible. La corde repose dans l'herbe. Victorino regarde encore la feuille. Tu as fini de sauter ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,10 +1740,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gabrielle a su inviter. Elle a accepté le non. Maman a vu. Un non est possible.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila a demandé.
+narrateur|C'est inviter.
+narrateur|Victorino a dit non.
+narrateur|Mila a accepté le non.
+maman|Tu as su inviter.
+maman|Tu as su accepter un non.
+maman|Bravo, Mila.
+enfant-f|J'ai dit d'accord.
+maman|Oui.
+maman|Un non, c'est possible.
+narrateur|La corde repose dans l'herbe.
+narrateur|Victorino regarde encore la feuille.
+maman|Tu as fini de sauter ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gabrielle range la corde. Maman lui tend le sac.</t>
+          <t>Mila enroule la corde. Le bois des poignées est lisse. On la met dans le sac. Les pots sont encore chauds. La cerise est trop haute. Oui. On la laisse. Le goûter est prêt. Vous venez ? Oui, papa. Tu as fini d'enrouler la corde ? Oui. Ils quittent le cerisier. La coccinelle reste sur la feuille.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1843,10 +1916,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gabrielle range la corde. Maman lui tend le sac.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Mila enroule la corde.
+narrateur|Le bois des poignées est lisse.
+maman|On la met dans le sac.
+narrateur|Les pots sont encore chauds.
+enfant-f|La cerise est trop haute.
+maman|Oui.
+maman|On la laisse.
+papa|Le goûter est prêt.
+papa|Vous venez ?
+enfant-f|Oui, papa.
+maman|Tu as fini d'enrouler la corde ?
+enfant-f|Oui.
+narrateur|Ils quittent le cerisier.
+narrateur|La coccinelle reste sur la feuille.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mila a invité. Elle a accepté un non. La corde est dans le sac. Bravo, Mila. Bravo. On goûte ? Oui. On goûte. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2011,10 +2096,17 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Mila a invité.
+narrateur|Elle a accepté un non.
+narrateur|La corde est dans le sac.
+maman|Bravo, Mila.
+papa|Bravo.
+enfant-f|On goûte ?
+papa|Oui.
+papa|On goûte.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une cerise bien rouge pend au cerisier. Les pots en terre sont chauds. Une coccinelle marche sur une feuille. L'arrosoir de maman goutte encore. Une goutte fait un rond dans la terre. Ça sent la terre mouillée. Mila, tu as vu la cerise ? Elle est toute rouge. Oui. Elle est trop haute. En ce moment, Mila tient une corde. La corde est un peu rêche. Les poignées sont en bois lisse. Je veux sauter. On saute dans l'herbe, d'accord. Victorino est sous le cerisier. Il regarde la coccinelle. La feuille tremble un peu. Tu peux inviter. Inviter, c'est demander. Mila va vers lui. Tu veux jouer avec nous ? Victorino secoue la tête. Non. Mila s'arrête. La corde reste dans ses mains. Maman pose l'arrosoir. On peut accepter un non. Accepter un non, c'est possible. D'accord. Mila reste dans l'herbe. Elle saute avec maman. La corde claque doucement. L'herbe est fraîche sous les pieds. Tu sautes bien. Ça fait un bruit. Oui. Un petit clac. Victorino reste sous le cerisier. La coccinelle avance encore. Mila accepte le non. Victorino reste tranquille. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On saute encore un peu ? Oui, maman. Une autre goutte tombe. Ça sent toujours la terre. Tu as fini de sauter ? Oui. Bravo. Tu as fait du bon travail. Mila pose la corde. La cerise pend encore, bien rouge.</t>
+          <t>Une cerise bien rouge pend au cerisier. Les pots en terre sont chauds. Une coccinelle marche sur une feuille. L'arrosoir de maman goutte encore. Une goutte fait un rond dans la terre. Ça sent la terre mouillée. Mila, tu as vu la cerise ? Elle est toute rouge. Oui. Elle est trop haute. En ce moment, Mila tient une corde. La corde est un peu rêche. Les poignées sont en bois lisse. Je veux sauter. On saute dans l'herbe, d'accord. Victorino est sous le cerisier. Il regarde la coccinelle. La feuille tremble un peu. Tu peux inviter. Inviter, c'est demander. Mila va vers lui. Tu veux jouer avec nous ? Victorino secoue la tête. Non. Mila s'arrête. La corde reste dans ses mains. Maman pose l'arrosoir. On peut accepter un non. Accepter un non, c'est possible. D'accord. Mila reste dans l'herbe. Elle saute avec maman. La corde claque doucement. L'herbe est fraîche sous les pieds. Tu sautes bien. Ça fait un bruit. Oui. Un petit clac. Victorino reste sous le cerisier. La coccinelle avance encore. Mila accepte le non. Victorino reste tranquille. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On saute encore un peu ? Oui, maman. Une autre goutte tombe. Ça sent toujours la terre. Tu as fini de sauter ? Oui. Bravo. Mila pose la corde. La cerise pend encore, bien rouge.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabrielle est dans le jardin. Maman est près des pots. Gabrielle a une corde à sauter. Noé est près du cerisier. Gabrielle va vers lui. Elle dit : tu veux jouer avec nous ? &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;, c'est demander. Noé dit : non. Gabrielle s'arrête. Elle accepte le non. Un non est possible. Maman dit : tu as su inviter. Tu as su accepter un non. Parce qu'elle accepte, Noé reste tranquille. Gabrielle saute seule. La corde claque doucement. Plus tard, Iris passe. Gabrielle invite encore. Iris dit : oui. Elles sautent. Le non de Noé est entendu. Papa les rejoindra pour le goûter.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une cerise bien rouge pend au cerisier. Les pots en terre sont chauds. Une coccinelle marche sur une feuille. L'arrosoir de maman goutte encore. Une goutte fait un rond dans la terre. Ça sent la terre mouillée. Mila, tu as vu la cerise ? Elle est toute rouge. Oui. Elle est trop haute. En ce moment, Mila tient une corde. La corde est un peu rêche. Les poignées sont en bois lisse. Je veux sauter. On saute dans l'herbe, d'accord. Victorino est sous le cerisier. Il regarde la coccinelle. La feuille tremble un peu. Tu peux inviter. Inviter, c'est demander. Mila va vers lui. Tu veux jouer avec nous ? Victorino secoue la tête. Non. Mila s'arrête. La corde reste dans ses mains. Maman pose l'arrosoir. On peut accepter un non. Accepter un non, c'est possible. D'accord. Mila reste dans l'herbe. Elle saute avec maman. La corde claque doucement. L'herbe est fraîche sous les pieds. Tu sautes bien. Ça fait un bruit. Oui. Un petit clac. Victorino reste sous le cerisier. La coccinelle avance encore. Mila accepte le non. Victorino reste tranquille. Merci. Tu as su inviter. Tu as su accepter un non. Il a dit non. Un non, c'est possible. On saute encore un peu ? Oui, maman. Une autre goutte tombe. Ça sent toujours la terre. Tu as fini de sauter ? Oui. Bravo. Mila pose la corde. La cerise pend encore, bien rouge.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1378,7 +1378,6 @@
 maman|Tu as fini de sauter ?
 enfant-f|Oui.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Mila pose la corde.
 narrateur|La cerise pend encore, bien rouge.</t>
         </is>
@@ -1417,7 +1416,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé dit non. Que fait Gabrielle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino dit non. Que fait Mila ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabrielle a su &lt;emphasis level="moderate"&gt;inviter&lt;/emphasis&gt;. Elle a accepté le non. Maman a vu. Un non est possible.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a demandé. C'est inviter. Victorino a dit non. Mila a accepté le non. Tu as su inviter. Tu as su accepter un non. Bravo, Mila. J'ai dit d'accord. Oui. Un non, c'est possible. La corde repose dans l'herbe. Victorino regarde encore la feuille. Tu as fini de sauter ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1785,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gabrielle range la corde. Maman lui tend le sac.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila enroule la corde. Le bois des poignées est lisse. On la met dans le sac. Les pots sont encore chauds. La cerise est trop haute. Oui. On la laisse. Le goûter est prêt. Vous venez ? Oui, papa. Tu as fini d'enrouler la corde ? Oui. Ils quittent le cerisier. La coccinelle reste sur la feuille.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1956,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mila a invité. Elle a accepté un non. La corde est dans le sac. Bravo, Mila. Bravo. On goûte ? Oui. On goûte. L'histoire est finie.</t>
+          <t>Mila a invité. Elle a accepté un non. La corde est dans le sac. Bravo, Mila. Bravo. On goûte ? Oui. On goûte.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mila a invité. Elle a accepté un non. La corde est dans le sac. Bravo, Mila. Bravo. On goûte ? Oui. On goûte.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,8 +2102,7 @@
 papa|Bravo.
 enfant-f|On goûte ?
 papa|Oui.
-papa|On goûte.
-narrateur|L'histoire est finie.</t>
+papa|On goûte.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2170,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.AMI.001-08.xlsx
+++ b/stories/arbres/ATOM-REL.AMI.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gabrielle, Noé, Iris, maman</t>
+          <t>Mila, Victorino, maman, papa</t>
         </is>
       </c>
     </row>
